--- a/output/pdf_financials_xlsx/ZIGY.xlsx
+++ b/output/pdf_financials_xlsx/ZIGY.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="24">
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="28">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="30">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>7.679437</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>7.740242</v>
       </c>
     </row>
     <row r="93">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="100">
@@ -2774,7 +2774,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>7.679437</v>
       </c>
@@ -3836,10 +3840,10 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.642012</v>
+        <v>-0.642012</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>1.13675</v>
+        <v>-1.13675</v>
       </c>
     </row>
     <row r="62">

--- a/output/pdf_financials_xlsx/ZIGY.xlsx
+++ b/output/pdf_financials_xlsx/ZIGY.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1.290135</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1.445144</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-1.290135</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-1.445144</v>
       </c>
     </row>
     <row r="12">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.730168</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.971403</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.9264</v>
+        <v>3.656568</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.035</v>
+        <v>3.006403</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.943249</v>
+        <v>0.213081</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.142692</v>
+        <v>0.171289</v>
       </c>
     </row>
     <row r="49">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
